--- a/data/invalidated/dataset_hospitales_rechazados.xlsx
+++ b/data/invalidated/dataset_hospitales_rechazados.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rut_paciente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fecha_nacimiento</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prevision</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>id_atencion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fecha_atencion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tipo_atencion</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>codigo_cie10</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>codigo_minsal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dosis_prescrita</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>alergia_principio</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>id_examen</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>codigo_examen</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>resultado_valor</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>unidad_medida</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>motivo_rechazo</t>
         </is>

--- a/data/invalidated/dataset_hospitales_rechazados.xlsx
+++ b/data/invalidated/dataset_hospitales_rechazados.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,87 +429,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rut_paciente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fecha_nacimiento</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prevision</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_atencion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>fecha_atencion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tipo_atencion</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>codigo_cie10</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>codigo_minsal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dosis_prescrita</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>alergia_principio</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>id_examen</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>codigo_examen</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>resultado_valor</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>unidad_medida</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>motivo_rechazo</t>
         </is>

--- a/data/invalidated/dataset_hospitales_rechazados.xlsx
+++ b/data/invalidated/dataset_hospitales_rechazados.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,91 +413,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rut_paciente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fecha_nacimiento</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prevision</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>id_atencion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fecha_atencion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tipo_atencion</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>codigo_cie10</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>codigo_minsal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dosis_prescrita</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>alergia_principio</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>id_examen</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>codigo_examen</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>resultado_valor</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>unidad_medida</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>motivo_rechazo</t>
         </is>
@@ -518,57 +506,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15111296-0</t>
+          <t>6813630-0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Isidora Camila Fuentes Sepulveda</t>
+          <t>Jorge Felipe Tapia Sepulveda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1965-09-22</t>
+          <t>1969-04-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02ed6200-5e4f-40e9-b78d-cee9afcca6a4</t>
+          <t>41960e19-e46a-4bb2-898c-f2878d0867f5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-31 18:11:24</t>
+          <t>2025-09-07 18:11:24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HOSPITALIZACION</t>
+          <t>PROCEDIMIENTO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>M54.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>200mg</t>
+          <t>100mg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -578,18 +566,18 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>23d7527e-ae2c-4864-9496-f590f41171ea</t>
+          <t>edab7512-dc5e-4eb7-8f0a-6d9adf35409b</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>302047</v>
+        <v>301045</v>
       </c>
       <c r="O2" t="n">
-        <v>64.31999999999999</v>
+        <v>57.23</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>U/L</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -601,57 +589,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15200589-0</t>
+          <t>9037267-0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ana Maria Gonzalez Diaz</t>
+          <t>Juan Felipe Gonzalez Rodriguez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2001-11-18</t>
+          <t>1964-04-14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>FONASA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>814885f7-5c6c-4a68-9f7f-cef954345058</t>
+          <t>b6b1a716-b7d5-4bca-b48b-410e7a8f34e3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2024-01-14 18:11:24</t>
+          <t>2026-03-17 18:13:27</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HOSPITALIZACION</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>J00</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>400mg</t>
+          <t>500mg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -661,14 +649,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ca4f7eb8-7c50-4a02-bc26-69cc93d2a6ae</t>
+          <t>7b9dc607-6ac5-4c77-849c-ba87170971c6</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>301001</v>
+        <v>301004</v>
       </c>
       <c r="O3" t="n">
-        <v>130.04</v>
+        <v>10.82</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -684,17 +672,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15712725-0</t>
+          <t>22724352-0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Juan Juan Rojas Silva</t>
+          <t>Carlos Jorge Perez Torres</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1998-04-28</t>
+          <t>2012-10-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -704,32 +692,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAPREDENA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>b999580e-5d15-43d8-8d03-4599971cf74f</t>
+          <t>e8f8f77a-2680-4ff5-b159-6817e29a4a6b</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-08-12 18:11:24</t>
+          <t>2025-11-06 18:13:27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>URGENCIA</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>A09.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -744,18 +732,18 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3e9b5a0b-467a-4bf8-91c7-6e3960499c7b</t>
+          <t>e032cd86-ef92-4f4b-bb61-336e2f72a5fc</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>302076</v>
+        <v>301001</v>
       </c>
       <c r="O4" t="n">
-        <v>59.76</v>
+        <v>50.91</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t>mmol/L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -767,17 +755,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6813630-0</t>
+          <t>7040477-0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jorge Felipe Tapia Sepulveda</t>
+          <t>Tomas Matias Martinez Morales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1969-04-29</t>
+          <t>1995-02-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -787,17 +775,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ISAPRE</t>
+          <t>FONASA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41960e19-e46a-4bb2-898c-f2878d0867f5</t>
+          <t>24b12777-d2ce-49b4-ab44-cec1fcab459e</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-09-07 18:11:24</t>
+          <t>2024-09-04 18:11:24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -812,33 +800,33 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M004</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100mg</t>
+          <t>200mg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Omeprazol</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>edab7512-dc5e-4eb7-8f0a-6d9adf35409b</t>
+          <t>b5dadbbd-1479-4980-b92a-a74782be225e</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>301045</v>
+        <v>302076</v>
       </c>
       <c r="O5" t="n">
-        <v>57.23</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -850,17 +838,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10649276-0</t>
+          <t>15712725-0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matias Gabriel Tapia Martinez</t>
+          <t>Juan Juan Rojas Silva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1952-08-29</t>
+          <t>1998-04-28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -870,37 +858,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>CAPREDENA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58a24b9d-867a-4b4e-99cb-27d469820a50</t>
+          <t>df79d8f0-ac2c-4044-b9f9-5d305903b7f3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-10-03 18:11:24</t>
+          <t>2024-11-09 18:13:27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOSPITALIZACION</t>
+          <t>URGENCIA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>E11.9</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>400mg</t>
+          <t>100mg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -910,14 +898,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>601329e8-f8a8-433b-b39a-6475ace93236</t>
+          <t>a5f1db5d-29b3-4c55-81b8-7ee12f34e7ea</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>301045</v>
+        <v>302076</v>
       </c>
       <c r="O6" t="n">
-        <v>51.61</v>
+        <v>59.76</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -933,37 +921,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7040477-0</t>
+          <t>9019271-0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomas Matias Martinez Morales</t>
+          <t>Fernanda Sofia Silva Diaz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1995-02-17</t>
+          <t>1960-04-26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FONASA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24b12777-d2ce-49b4-ab44-cec1fcab459e</t>
+          <t>2f515b17-af01-46d4-8e41-3d1c0da34a90</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2024-09-04 18:11:24</t>
+          <t>2026-02-08 18:11:24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -973,34 +961,34 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>M54.5</t>
+          <t>A09.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>200mg</t>
+          <t>300mg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Omeprazol</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>b5dadbbd-1479-4980-b92a-a74782be225e</t>
+          <t>802af244-ccd5-4336-86e6-b687bd147df3</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>302076</v>
+        <v>301045</v>
       </c>
       <c r="O7" t="n">
-        <v>81.40000000000001</v>
+        <v>60.69</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1016,47 +1004,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9019271-0</t>
+          <t>21609705-0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fernanda Sofia Silva Diaz</t>
+          <t>Jorge Felipe Martinez Martinez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1960-04-26</t>
+          <t>1955-07-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ISAPRE</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2f515b17-af01-46d4-8e41-3d1c0da34a90</t>
+          <t>379b2b68-b51a-4678-bbca-14d4b5406fea</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-02-08 18:11:24</t>
+          <t>2025-08-24 18:13:27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO</t>
+          <t>HOSPITALIZACION</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A09.9</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1066,7 +1054,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>300mg</t>
+          <t>400mg</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1076,18 +1064,18 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>802af244-ccd5-4336-86e6-b687bd147df3</t>
+          <t>0c0cae04-d422-4623-8970-ed7047d1bde2</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>301045</v>
+        <v>302076</v>
       </c>
       <c r="O8" t="n">
-        <v>60.69</v>
+        <v>51.14</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t>U/L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1182,17 +1170,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12345678-9</t>
+          <t>9019271-0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sofia Antonia Torres Gonzalez</t>
+          <t>Fernanda Sofia Silva Diaz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
+          <t>1960-04-26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1207,17 +1195,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>b13f2648-07bb-48f2-b7ae-a225eda496c7</t>
+          <t>daabdf5e-35e6-480a-a8b2-fb4e1dcaaf01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2024-06-19 18:11:24</t>
+          <t>2026-04-19 18:13:27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CONSULTA</t>
+          <t>PROCEDIMIENTO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1227,7 +1215,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1242,14 +1230,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ae68b921-f6f1-4ef1-8a94-8555782f5960</t>
+          <t>c5aa522a-4a45-48aa-9d54-666a6113a6ba</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>302047</v>
+        <v>301045</v>
       </c>
       <c r="O10" t="n">
-        <v>74.04000000000001</v>
+        <v>60.69</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1265,17 +1253,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12105048-0</t>
+          <t>12540538-0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jorge Felipe Silva Contreras</t>
+          <t>Tomas Roberto Rodriguez Lopez</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1963-01-12</t>
+          <t>1991-06-13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1285,32 +1273,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ISAPRE</t>
+          <t>DIPRECA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>a5d86296-eaea-4c51-af1e-5acb19c5fe72</t>
+          <t>dc7aef43-be9d-4ae1-b955-af69bdb0702b</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-02-24 18:11:24</t>
+          <t>2025-02-02 18:13:27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CONSULTA</t>
+          <t>PROCEDIMIENTO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ZZZ99</t>
+          <t>A09.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MED-FALSO</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1325,14 +1313,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fecf6fcf-0e52-4913-b18e-627a1e79a763</t>
+          <t>5f308759-b425-4313-829d-5ae0d37bb0cf</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>302047</v>
+        <v>301004</v>
       </c>
       <c r="O11" t="n">
-        <v>48.83</v>
+        <v>16.61</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1341,44 +1329,44 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+          <t>RUT_DIGITO_INVALIDO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20424662-9</t>
+          <t>12584989-0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roberto Gabriel Sepulveda Lopez</t>
+          <t>Isidora Camila Morales Hernandez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1995-08-23</t>
+          <t>1969-05-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAPREDENA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>eb491095-dd56-40bf-9764-2ace8bb56afa</t>
+          <t>a1f3ca80-5c73-4da1-9d55-0550a213aeb2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2050-05-12 10:00:00</t>
+          <t>2026-02-15 18:13:27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1403,19 +1391,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Ibuprofeno</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ec04937c-9842-4764-b483-de27123926fc</t>
+          <t>ecfa3724-a7f8-4acf-9182-51526ef9b67c</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>301045</v>
+        <v>301004</v>
       </c>
       <c r="O12" t="n">
-        <v>107.77</v>
+        <v>82.84</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1424,24 +1412,24 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>FECHA_ATENCION_FUTURA</t>
+          <t>RUT_DIGITO_INVALIDO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12540538-0</t>
+          <t>8142778-0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tomas Roberto Rodriguez Lopez</t>
+          <t>Diego Luis Morales Contreras</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1991-06-13</t>
+          <t>2010-06-04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1451,37 +1439,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DIPRECA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9cdf26ae-27f9-42e9-b8f7-4439218ebd34</t>
+          <t>4cf260e5-06f5-4639-b539-751c40056ce6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2025-02-07 18:11:24</t>
+          <t>2026-03-05 18:13:27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A09.9</t>
+          <t>J00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>200mg</t>
+          <t>100mg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1491,18 +1479,18 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>c28095d7-bba5-4209-9cac-87511c7dd796</t>
+          <t>086a8ff4-af70-48b6-a679-48be9523db65</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>301004</v>
+        <v>302076</v>
       </c>
       <c r="O13" t="n">
-        <v>16.61</v>
+        <v>18.94</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1514,57 +1502,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21609705-0</t>
+          <t>12345678-9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jorge Felipe Martinez Martinez</t>
+          <t>Sofia Antonia Torres Gonzalez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1955-07-14</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>04a72892-5524-4430-bc82-884cd58387ff</t>
+          <t>b13f2648-07bb-48f2-b7ae-a225eda496c7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023-08-29 18:11:24</t>
+          <t>2024-06-19 18:11:24</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HOSPITALIZACION</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>A09.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>M004</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>400mg</t>
+          <t>300mg</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1574,18 +1562,18 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ba64c08e-9ee7-40a4-9d1c-09991b5bdc05</t>
+          <t>ae68b921-f6f1-4ef1-8a94-8555782f5960</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>302076</v>
+        <v>302047</v>
       </c>
       <c r="O14" t="n">
-        <v>51.14</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1597,22 +1585,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12584989-0</t>
+          <t>6813630-0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isidora Camila Morales Hernandez</t>
+          <t>Jorge Felipe Tapia Sepulveda</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1969-05-10</t>
+          <t>1969-04-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1622,12 +1610,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>96ac25e9-ede8-48ad-aba5-c4a62ee1561d</t>
+          <t>9922fabd-c2b0-4420-8e07-15b084d53016</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2024-08-29 18:11:24</t>
+          <t>2026-02-15 18:13:27</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1642,29 +1630,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>300mg</t>
+          <t>100mg</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ibuprofeno</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6df921be-c349-4de5-b929-85456064dd60</t>
+          <t>b73c55e7-83e2-4c08-9c9e-4e072cbd80df</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>301004</v>
+        <v>301045</v>
       </c>
       <c r="O15" t="n">
-        <v>82.84</v>
+        <v>57.23</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1680,17 +1668,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8142778-0</t>
+          <t>22724352-0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diego Luis Morales Contreras</t>
+          <t>Carlos Jorge Perez Torres</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2010-06-04</t>
+          <t>2012-10-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1705,12 +1693,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3e40770f-fe3b-4b5a-a0c9-89ca1ffb8d9c</t>
+          <t>2910c598-f86a-4ce4-9707-e32b744c5ccc</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2025-06-27 18:11:24</t>
+          <t>2025-02-26 18:11:24</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1720,12 +1708,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>J00</t>
+          <t>A09.9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1740,18 +1728,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>a1ecdfae-ee37-4092-bb8c-df2d051c5348</t>
+          <t>55057ea7-9bab-40f5-add3-9b47b96f6806</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>302076</v>
+        <v>301001</v>
       </c>
       <c r="O16" t="n">
-        <v>18.94</v>
+        <v>50.91</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t>mmol/L</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1763,17 +1751,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6080138-0</t>
+          <t>8142778-0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diego Tomas Soto Contreras</t>
+          <t>Diego Luis Morales Contreras</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1989-04-12</t>
+          <t>2010-06-04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1783,37 +1771,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CAPREDENA</t>
+          <t>ISAPRE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>732f02b7-e694-4026-90f3-0d8e524922bf</t>
+          <t>b4950897-52a6-4564-9e81-d5b90ea76690</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024-08-09 18:11:24</t>
+          <t>2025-11-20 18:13:27</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>URGENCIA</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>J00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>200mg</t>
+          <t>100mg</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1823,18 +1811,18 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7d079ffc-5412-4be1-8242-1069d4846b75</t>
+          <t>1d6b41ec-a9cb-446f-bdcc-ab804373c76c</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>301045</v>
+        <v>302076</v>
       </c>
       <c r="O17" t="n">
-        <v>125.59</v>
+        <v>18.94</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1846,42 +1834,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22398049-0</t>
+          <t>21609705-0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Antonia Javiera Martinez Morales</t>
+          <t>Jorge Felipe Martinez Martinez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1960-05-10</t>
+          <t>1955-07-14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ISAPRE</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02738e5e-e96b-4c23-9aa6-c5ace795813b</t>
+          <t>5aa0ad66-2b57-4b0e-9acd-1d3f9d3def33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2025-10-24 18:11:24</t>
+          <t>2025-02-10 18:13:27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>URGENCIA</t>
+          <t>HOSPITALIZACION</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1891,12 +1879,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>100mg</t>
+          <t>400mg</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1906,14 +1894,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>79bf516b-d3b0-4aad-b0ca-20b499722ae8</t>
+          <t>00321a0e-78e4-4888-a3e8-bf574febcefe</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>301004</v>
+        <v>302076</v>
       </c>
       <c r="O18" t="n">
-        <v>32.44</v>
+        <v>51.14</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1929,37 +1917,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23011319-0</t>
+          <t>20424662-9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camila Javiera Contreras Morales</t>
+          <t>Roberto Gabriel Sepulveda Lopez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1991-11-25</t>
+          <t>1995-08-23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>CAPREDENA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0c2fae79-87b3-43f6-af07-fc90cfa21437</t>
+          <t>eb491095-dd56-40bf-9764-2ace8bb56afa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2023-09-24 18:11:24</t>
+          <t>2050-05-12 10:00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1969,17 +1957,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>J00</t>
+          <t>M54.5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>500mg</t>
+          <t>300mg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1989,40 +1977,40 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9a02fe2e-e694-481e-92af-7957466ce3f9</t>
+          <t>ec04937c-9842-4764-b483-de27123926fc</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>302047</v>
+        <v>301045</v>
       </c>
       <c r="O19" t="n">
-        <v>78.29000000000001</v>
+        <v>107.77</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>U/L</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>RUT_DIGITO_INVALIDO</t>
+          <t>FECHA_ATENCION_FUTURA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14971099-0</t>
+          <t>15056901-0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Antonia Camila Contreras Tapia</t>
+          <t>Isidora Sofia Torres Sepulveda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2002-11-19</t>
+          <t>1972-06-25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2032,58 +2020,58 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>CAPREDENA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11ad7ded-5158-4571-ac3f-f650fedc6257</t>
+          <t>73e5a30d-80ef-4478-9ea7-6264ed253ab4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-01-06 18:11:24</t>
+          <t>2024-10-29 18:13:27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>URGENCIA</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>J00</t>
+          <t>K21.9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>100mg</t>
+          <t>300mg</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Ibuprofeno</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4e15401c-052b-4b17-a702-4b2272f1ca6a</t>
+          <t>b03d23d1-29ff-4f8a-a6dc-f0239f4d90b3</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>302076</v>
+        <v>301001</v>
       </c>
       <c r="O20" t="n">
-        <v>134.52</v>
+        <v>48.46</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>mmol/L</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2095,57 +2083,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9037267-0</t>
+          <t>15200589-0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan Felipe Gonzalez Rodriguez</t>
+          <t>Ana Maria Gonzalez Diaz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1964-04-14</t>
+          <t>2001-11-18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FONASA</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>b992bcb2-8360-42e8-961e-c077a2a08da8</t>
+          <t>814885f7-5c6c-4a68-9f7f-cef954345058</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-01-06 18:11:24</t>
+          <t>2024-01-14 18:11:24</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONSULTA</t>
+          <t>HOSPITALIZACION</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>J00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>500mg</t>
+          <t>400mg</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2155,14 +2143,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>4dc56b96-c3b5-401f-95c7-6ac1e2bbab49</t>
+          <t>ca4f7eb8-7c50-4a02-bc26-69cc93d2a6ae</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>301004</v>
+        <v>301001</v>
       </c>
       <c r="O21" t="n">
-        <v>10.82</v>
+        <v>130.04</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2178,22 +2166,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8329910-0</t>
+          <t>9037267-0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ana Daniela Martinez Fuentes</t>
+          <t>Juan Felipe Gonzalez Rodriguez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1969-03-12</t>
+          <t>1964-04-14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2203,27 +2191,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>c310b906-b1e4-4aaa-b365-2a69e474c832</t>
+          <t>b3499a4c-b8ec-4dd1-94e2-2118b742ed7c</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2024-04-12 18:11:24</t>
+          <t>2025-11-08 18:13:27</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>URGENCIA</t>
+          <t>CONSULTA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>K21.9</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2238,14 +2226,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>e7f2ebc0-a005-41d2-a142-bd17e42b228b</t>
+          <t>409e93e1-4edc-4c2e-ae68-41666778e5a2</t>
         </is>
       </c>
       <c r="N22" t="n">
         <v>301004</v>
       </c>
       <c r="O22" t="n">
-        <v>58</v>
+        <v>10.82</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2261,81 +2249,3733 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>12105048-0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Silva Contreras</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1963-01-12</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>f6907a29-173e-4e91-9ea8-68e45e946ce6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-10-11 18:13:27</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ZZZ99</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MED-FALSO</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>67c9229f-a09f-4405-8577-c5fc5d2f628e</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O23" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15712725-0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Juan Juan Rojas Silva</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1998-04-28</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CAPREDENA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>b999580e-5d15-43d8-8d03-4599971cf74f</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-08-12 18:11:24</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3e9b5a0b-467a-4bf8-91c7-6e3960499c7b</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O24" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10649276-0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Matias Gabriel Tapia Martinez</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1952-08-29</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>58a24b9d-867a-4b4e-99cb-27d469820a50</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-10-03 18:11:24</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>E11.9</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>601329e8-f8a8-433b-b39a-6475ace93236</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O25" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>8142778-0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Diego Luis Morales Contreras</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>f7fc70f4-17eb-42e0-b78e-d350194465ff</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2024-08-16 18:13:27</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>fa091247-ad46-45d5-b558-a1ec78b9df69</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O26" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8142778-0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Diego Luis Morales Contreras</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3e40770f-fe3b-4b5a-a0c9-89ca1ffb8d9c</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-06-27 18:11:24</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>a1ecdfae-ee37-4092-bb8c-df2d051c5348</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O27" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6080138-0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Diego Tomas Soto Contreras</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1989-04-12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CAPREDENA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>732f02b7-e694-4026-90f3-0d8e524922bf</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2024-08-09 18:11:24</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>7d079ffc-5412-4be1-8242-1069d4846b75</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O28" t="n">
+        <v>125.59</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>9019271-0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fernanda Sofia Silva Diaz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1960-04-26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>52621d97-61f1-460c-bb77-ae0062438863</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2024-12-17 18:13:27</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>5e7ae62f-570d-4a7e-9460-9132c6fe86b0</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O29" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6813630-0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Tapia Sepulveda</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1969-04-29</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>99ceb09b-1784-4a63-bb12-b6ab852d25a9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-02-28 18:13:27</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6d23c457-3d36-405d-9e3c-0fe0053f412d</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O30" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10649276-0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Matias Gabriel Tapia Martinez</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1952-08-29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ca456d8f-ba73-45ae-8e56-110e90786ee1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-11-12 18:13:27</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>E11.9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>e13886ab-6635-46c0-826d-aa1b24fdd362</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O31" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14971099-0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Antonia Camila Contreras Tapia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2002-11-19</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>e52542d4-e7c4-4930-a781-5d83eb6cc3f5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:13:27</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>573ef5fc-ff7e-4494-9580-3a973b2d206a</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O32" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>23011319-0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Camila Javiera Contreras Morales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1991-11-25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>67213039-63d0-4dc1-9410-23e4aa75dcea</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-03-13 18:13:27</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>f6287870-59f9-4748-bcfb-cfb601c451b4</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O33" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>23011319-0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camila Javiera Contreras Morales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1991-11-25</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0c2fae79-87b3-43f6-af07-fc90cfa21437</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2023-09-24 18:11:24</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>9a02fe2e-e694-481e-92af-7957466ce3f9</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O34" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9019271-0</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fernanda Sofia Silva Diaz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1960-04-26</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>cd89d748-2118-44f7-8704-25eff86fc096</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-09-23 18:13:27</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>f2543286-cd39-42d1-a338-4ace262edbf1</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O35" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12105048-0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Silva Contreras</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1963-01-12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>d2403383-ac99-4fc5-a442-f1f142380c4c</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-08-10 18:13:27</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ZZZ99</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MED-FALSO</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6757f7f3-c3d5-4e34-bcc7-4fa31cb1ee2f</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O36" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6813630-0</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Tapia Sepulveda</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1969-04-29</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2799d887-5dfd-46e6-a157-dcadb4eec826</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-10-17 18:13:27</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1e4d4c32-b5aa-4665-b968-e352a60be428</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O37" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15200589-0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ana Maria Gonzalez Diaz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2001-11-18</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>9aa28e06-108d-4956-9dc1-9a69370626bd</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2024-09-20 18:13:27</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>fc0861f1-29a9-48e1-9472-5d162d5e386e</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>301001</v>
+      </c>
+      <c r="O38" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12105048-0</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Silva Contreras</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1963-01-12</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>a5d86296-eaea-4c51-af1e-5acb19c5fe72</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-02-24 18:11:24</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ZZZ99</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MED-FALSO</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>fecf6fcf-0e52-4913-b18e-627a1e79a763</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O39" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9019271-0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fernanda Sofia Silva Diaz</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1960-04-26</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>a932ce2d-770a-43de-b4cf-a6f08dd155b2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2024-07-25 18:13:27</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2f2a72ea-8b72-4998-9ade-5ea94afedfb2</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O40" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>21609705-0</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Martinez Martinez</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1955-07-14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>d58636cc-4b5f-4cd5-9a56-e398788eb6d2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-08-21 18:13:27</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>bdbe08f1-0cd6-499d-931a-600003ad9e5c</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O41" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15200589-0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ana Maria Gonzalez Diaz</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2001-11-18</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77f14426-e7a8-4603-bef5-9cff1ff961c6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-09-10 18:13:27</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2578e50e-0da0-4512-a26b-04060fbffeb8</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>301001</v>
+      </c>
+      <c r="O42" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12584989-0</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Isidora Camila Morales Hernandez</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1969-05-10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6a0ba6dd-9468-4164-8c6f-c2b2336a867d</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-10-24 18:13:27</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Ibuprofeno</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>a51954cf-0294-40e7-a1b8-6121df876df9</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O43" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14971099-0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Antonia Camila Contreras Tapia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2002-11-19</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11ad7ded-5158-4571-ac3f-f650fedc6257</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-01-06 18:11:24</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4e15401c-052b-4b17-a702-4b2272f1ca6a</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O44" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12540538-0</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tomas Roberto Rodriguez Lopez</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1991-06-13</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DIPRECA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>9cdf26ae-27f9-42e9-b8f7-4439218ebd34</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-02-07 18:11:24</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>c28095d7-bba5-4209-9cac-87511c7dd796</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O45" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9037267-0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Juan Felipe Gonzalez Rodriguez</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1964-04-14</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FONASA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>b992bcb2-8360-42e8-961e-c077a2a08da8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-01-06 18:11:24</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4dc56b96-c3b5-401f-95c7-6ac1e2bbab49</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O46" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6813630-0</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Tapia Sepulveda</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1969-04-29</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4e7a1539-360d-4626-9747-320fc2a4c032</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:13:27</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>dce0299f-a345-422c-93ef-2b0a5d835503</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O47" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>22724352-0</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Carlos Jorge Perez Torres</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2012-10-30</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>ISAPRE</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2910c598-f86a-4ce4-9707-e32b744c5ccc</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2025-02-26 18:11:24</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>efc43b37-4731-4b5d-a951-64af0699d570</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:13:27</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>CONSULTA</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>A09.9</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>M002</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>100mg</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>55057ea7-9bab-40f5-add3-9b47b96f6806</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>656dd981-b289-4acb-b534-7a0a7a1bfe6a</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
         <v>301001</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O48" t="n">
         <v>50.91</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>mmol/L</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>21609705-0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Martinez Martinez</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1955-07-14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>04a72892-5524-4430-bc82-884cd58387ff</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2023-08-29 18:11:24</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ba64c08e-9ee7-40a4-9d1c-09991b5bdc05</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O49" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8329910-0</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ana Daniela Martinez Fuentes</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1969-03-12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FONASA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>c310b906-b1e4-4aaa-b365-2a69e474c832</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2024-04-12 18:11:24</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>K21.9</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>e7f2ebc0-a005-41d2-a142-bd17e42b228b</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O50" t="n">
+        <v>58</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12345678-9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sofia Antonia Torres Gonzalez</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2014-10-20</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ae55fc07-7cc7-439b-b0c8-5062ebf445b1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:13:27</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>4a1da866-6e21-4d5a-b3c5-84da615b9ca3</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O51" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12584989-0</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Isidora Camila Morales Hernandez</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1969-05-10</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>96ac25e9-ede8-48ad-aba5-c4a62ee1561d</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2024-08-29 18:11:24</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>300mg</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Ibuprofeno</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>6df921be-c349-4de5-b929-85456064dd60</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O52" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8142778-0</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Diego Luis Morales Contreras</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>cd2cbc3b-d703-43a7-99ad-e86e56dfee9a</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-08-09 18:13:27</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>658649c1-c359-4027-806f-4b774278bd6d</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O53" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>23011319-0</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Camila Javiera Contreras Morales</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1991-11-25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>c93bd329-67c8-4845-8764-991b31765e43</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-01-06 18:13:27</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5fbad316-906c-48bf-8795-35d4aefe399b</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O54" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>22398049-0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Antonia Javiera Martinez Morales</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1960-05-10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>02738e5e-e96b-4c23-9aa6-c5ace795813b</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-10-24 18:11:24</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>79bf516b-d3b0-4aad-b0ca-20b499722ae8</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O55" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12540538-0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tomas Roberto Rodriguez Lopez</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1991-06-13</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DIPRECA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>986c4fd1-ef9b-4f70-8db9-ef041e911d95</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-01-22 18:13:27</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A09.9</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>e9d0dd04-9bb2-4520-ba99-5c6827d72be4</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O56" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>15712725-0</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Juan Juan Rojas Silva</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1998-04-28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CAPREDENA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>4a3953a4-9d4c-4ac2-9283-c5d9226f4db2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-12-11 18:13:27</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>6f80b4e5-829c-4389-96f7-cc6c2fc60662</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O57" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6813630-0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Tapia Sepulveda</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1969-04-29</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>c75e2f43-e164-4f91-96a3-b5bc921b4b90</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2024-11-16 18:13:27</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>24871e31-88b6-4463-b026-6527a621c02e</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>301045</v>
+      </c>
+      <c r="O58" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8142778-0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Diego Luis Morales Contreras</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>e1531c2e-a55a-40ff-b458-4f7d4e5385e8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2024-11-11 18:13:27</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>100mg</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>03213f8b-6a50-4741-a5d8-f940da8ce718</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O59" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>23011319-0</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Camila Javiera Contreras Morales</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1991-11-25</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>7c21fd66-4487-48b3-9747-71923e0d15f3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-02-14 18:13:27</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>7f62e73e-f08a-4d5f-9acf-3255231a3b25</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O60" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12105048-0</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Silva Contreras</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1963-01-12</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>800d7d29-d652-4358-82a6-08017a4d5c0b</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-07-16 18:13:27</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ZZZ99</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>MED-FALSO</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>5a552528-a409-496f-9244-a1b3e8527f18</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O61" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>21609705-0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Martinez Martinez</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1955-07-14</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>acabc28b-dca0-414b-8fc4-d0981724dfc6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2024-07-16 18:13:27</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ca883ad1-8a06-40a9-8f6b-bea682d09330</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>302076</v>
+      </c>
+      <c r="O62" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>15111296-0</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Isidora Camila Fuentes Sepulveda</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1965-09-22</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>02ed6200-5e4f-40e9-b78d-cee9afcca6a4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:11:24</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>23d7527e-ae2c-4864-9496-f590f41171ea</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O63" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8329910-0</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ana Daniela Martinez Fuentes</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1969-03-12</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FONASA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>314c7752-fe52-4f66-b480-042e1cfdc450</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-05-16 18:13:27</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>K21.9</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>76fa10a7-c5af-4003-9e62-ba450d9c4214</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O64" t="n">
+        <v>58</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12105048-0</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Jorge Felipe Silva Contreras</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1963-01-12</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ISAPRE</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>50919c17-4c0d-4080-b877-a69001be97e1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-03-14 18:13:27</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CONSULTA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ZZZ99</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>MED-FALSO</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>200mg</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>f3c6cd07-1369-428f-9cfc-eca964a193fb</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>302047</v>
+      </c>
+      <c r="O65" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>mmol/L</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO | CODIGO_CIE10_NO_EXISTE | CODIGO_MINSAL_FORMATO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>15200589-0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ana Maria Gonzalez Diaz</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2001-11-18</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>74c7063d-eb79-4325-88d0-6f468a202e76</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2024-07-11 18:13:27</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>HOSPITALIZACION</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>J00</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>400mg</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>19a62b3b-254a-499e-b9e4-645f74245d24</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>301001</v>
+      </c>
+      <c r="O66" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>RUT_DIGITO_INVALIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8329910-0</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ana Daniela Martinez Fuentes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1969-03-12</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FONASA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>7db37260-c2ba-4b52-aeed-39373fc51535</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:13:27</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>URGENCIA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>K21.9</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>500mg</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>ca8ff5db-d746-490f-a4e7-516362ff4274</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>301004</v>
+      </c>
+      <c r="O67" t="n">
+        <v>58</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>RUT_DIGITO_INVALIDO</t>
         </is>
